--- a/data/trans_orig/IP18A01-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP18A01-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1902</t>
+          <t>1941</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8771</t>
+          <t>8910</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2639</t>
+          <t>3176</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11389</t>
+          <t>10710</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6387</t>
+          <t>5997</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16601</t>
+          <t>15890</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,5%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>106774</t>
+          <t>106635</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>113643</t>
+          <t>113604</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>117608</t>
+          <t>118287</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>126358</t>
+          <t>125821</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>227941</t>
+          <t>228652</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>238155</t>
+          <t>238545</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,55%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7344</t>
+          <t>6929</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17286</t>
+          <t>17343</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6385</t>
+          <t>5983</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16193</t>
+          <t>15793</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15189</t>
+          <t>15085</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29917</t>
+          <t>28835</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,35%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>148067</t>
+          <t>148010</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>158009</t>
+          <t>158424</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>89,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>163723</t>
+          <t>164123</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>173531</t>
+          <t>173933</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>315352</t>
+          <t>316434</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>330080</t>
+          <t>330184</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,63%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9036</t>
+          <t>8676</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19279</t>
+          <t>19010</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8321</t>
+          <t>8557</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19094</t>
+          <t>19335</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19854</t>
+          <t>19868</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>34302</t>
+          <t>34879</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,5%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>105298</t>
+          <t>105567</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>115541</t>
+          <t>115901</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>84,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>114702</t>
+          <t>114461</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>125475</t>
+          <t>125239</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,73%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>224071</t>
+          <t>223494</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>238519</t>
+          <t>238505</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,72%</t>
+          <t>86,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,31%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15297</t>
+          <t>15140</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29831</t>
+          <t>29927</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16149</t>
+          <t>15598</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30223</t>
+          <t>30615</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>34365</t>
+          <t>34926</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>55677</t>
+          <t>55814</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,93%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>162712</t>
+          <t>162616</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>177246</t>
+          <t>177403</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>84,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>151083</t>
+          <t>150691</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>165157</t>
+          <t>165708</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,33%</t>
+          <t>83,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>318171</t>
+          <t>318034</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>339483</t>
+          <t>338922</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>90,66%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>41000</t>
+          <t>42169</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>62606</t>
+          <t>63698</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>41419</t>
+          <t>41648</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>64291</t>
+          <t>64459</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>87795</t>
+          <t>88837</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>118659</t>
+          <t>120141</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,83%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>535412</t>
+          <t>534320</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>557018</t>
+          <t>555849</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>89,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>559723</t>
+          <t>559555</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>582595</t>
+          <t>582366</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1103373</t>
+          <t>1101891</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1134237</t>
+          <t>1133195</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,73%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8822</t>
+          <t>7988</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20844</t>
+          <t>19867</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9349</t>
+          <t>9181</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22909</t>
+          <t>21963</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20275</t>
+          <t>20776</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>36862</t>
+          <t>38432</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,96%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>108254</t>
+          <t>109231</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>120276</t>
+          <t>121110</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>84,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>123225</t>
+          <t>124171</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>136785</t>
+          <t>136953</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>84,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>238370</t>
+          <t>236800</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>254957</t>
+          <t>254456</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>86,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,45%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8819</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21063</t>
+          <t>19534</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11710</t>
+          <t>12091</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26424</t>
+          <t>26087</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>23389</t>
+          <t>23358</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>40754</t>
+          <t>41197</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,43%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>169302</t>
+          <t>170831</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>181546</t>
+          <t>182066</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>89,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>178200</t>
+          <t>178537</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>192914</t>
+          <t>192533</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>87,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>354235</t>
+          <t>353792</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>371600</t>
+          <t>371631</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,09%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7830</t>
+          <t>7930</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18888</t>
+          <t>18422</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9276</t>
+          <t>8939</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21501</t>
+          <t>21275</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18778</t>
+          <t>20072</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>34384</t>
+          <t>34925</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,73%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>123175</t>
+          <t>123641</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>134233</t>
+          <t>134133</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,7%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>134094</t>
+          <t>134320</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>146319</t>
+          <t>146656</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>263274</t>
+          <t>262733</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>278880</t>
+          <t>277586</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>88,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,26%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18708</t>
+          <t>18549</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>35596</t>
+          <t>35401</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16527</t>
+          <t>16890</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31856</t>
+          <t>31987</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>39310</t>
+          <t>38874</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>61433</t>
+          <t>62497</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,49%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>166682</t>
+          <t>166877</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>183570</t>
+          <t>183729</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,4%</t>
+          <t>82,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>169453</t>
+          <t>169322</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>184782</t>
+          <t>184419</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,18%</t>
+          <t>84,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>91,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>342153</t>
+          <t>341089</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>364276</t>
+          <t>364712</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>84,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>90,37%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>52879</t>
+          <t>53923</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>77802</t>
+          <t>77796</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>57925</t>
+          <t>58366</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>84753</t>
+          <t>85503</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>118617</t>
+          <t>119009</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>156587</t>
+          <t>155819</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,36%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>586002</t>
+          <t>586008</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>610925</t>
+          <t>609881</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4185,7 +4185,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>622908</t>
+          <t>622158</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>649736</t>
+          <t>649295</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>87,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1214878</t>
+          <t>1215646</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1252848</t>
+          <t>1252456</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,32%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7574</t>
+          <t>6990</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19281</t>
+          <t>18788</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7468</t>
+          <t>7629</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18467</t>
+          <t>19007</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17497</t>
+          <t>17616</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33627</t>
+          <t>33983</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,16%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>103540</t>
+          <t>104033</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>115247</t>
+          <t>115831</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,3%</t>
+          <t>84,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>116872</t>
+          <t>116332</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>127871</t>
+          <t>127710</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>85,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>224533</t>
+          <t>224177</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>240663</t>
+          <t>240544</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>86,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,18%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9628</t>
+          <t>9142</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20876</t>
+          <t>20330</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12045</t>
+          <t>12888</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25153</t>
+          <t>26325</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>24873</t>
+          <t>24978</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>43134</t>
+          <t>41730</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,38%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>172442</t>
+          <t>172988</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>183690</t>
+          <t>184176</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>183577</t>
+          <t>182405</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>196685</t>
+          <t>195842</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>87,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>358914</t>
+          <t>360318</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>377175</t>
+          <t>377070</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>89,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,79%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7456</t>
+          <t>7948</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18519</t>
+          <t>19194</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7244</t>
+          <t>6619</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18956</t>
+          <t>17873</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16777</t>
+          <t>16982</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>32482</t>
+          <t>32225</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,54%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>117481</t>
+          <t>116806</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>128544</t>
+          <t>128052</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>124317</t>
+          <t>125400</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>136029</t>
+          <t>136654</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,77%</t>
+          <t>87,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>246791</t>
+          <t>247048</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>262496</t>
+          <t>262291</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,37%</t>
+          <t>88,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>93,92%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14718</t>
+          <t>14080</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29362</t>
+          <t>29003</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10730</t>
+          <t>10735</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23830</t>
+          <t>23266</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>27474</t>
+          <t>27951</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>47695</t>
+          <t>46624</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,58%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>158843</t>
+          <t>159202</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>173487</t>
+          <t>174125</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>84,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>158509</t>
+          <t>159073</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>171609</t>
+          <t>171604</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>87,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>322849</t>
+          <t>323920</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>343070</t>
+          <t>342593</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,46%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>48061</t>
+          <t>49014</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>73365</t>
+          <t>74082</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>47364</t>
+          <t>47953</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>70654</t>
+          <t>72760</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>102744</t>
+          <t>102758</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>138204</t>
+          <t>135141</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,32%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>566980</t>
+          <t>566263</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>592284</t>
+          <t>591331</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>599027</t>
+          <t>596921</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>622317</t>
+          <t>621728</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1171821</t>
+          <t>1174884</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1207281</t>
+          <t>1207267</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,7 +6197,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>89,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -6579,7 +6579,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4874</t>
+          <t>4602</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6649,7 +6649,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>5576</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,4%</t>
         </is>
       </c>
     </row>
@@ -6687,7 +6687,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12180</t>
+          <t>12452</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -6702,7 +6702,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,42%</t>
+          <t>73,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6757,7 +6757,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>33237</t>
+          <t>33144</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -6772,7 +6772,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>85,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>784</t>
+          <t>773</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5575</t>
+          <t>5784</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1581</t>
+          <t>1611</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7606</t>
+          <t>7357</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3148</t>
+          <t>3223</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10195</t>
+          <t>10568</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>13,43%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>23400</t>
+          <t>23191</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>28191</t>
+          <t>28202</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>80,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>42130</t>
+          <t>42379</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>48155</t>
+          <t>48125</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>85,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>68516</t>
+          <t>68143</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>75563</t>
+          <t>75488</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,05%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>95,91%</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4260</t>
+          <t>4259</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7280,7 +7280,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7300,7 +7300,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1867</t>
+          <t>2234</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7315,7 +7315,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>376</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4468</t>
+          <t>4814</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>8,31%</t>
         </is>
       </c>
     </row>
@@ -7373,7 +7373,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21976</t>
+          <t>21977</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>83,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -7408,7 +7408,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>29813</t>
+          <t>29446</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -7423,7 +7423,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>53449</t>
+          <t>53103</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>57527</t>
+          <t>57541</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,35%</t>
         </is>
       </c>
     </row>
@@ -7603,62 +7603,62 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>743</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>6127</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>8,22%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2,65%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>21,84%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>1186</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5948</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>8,22%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3592</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>4,16%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>21,21%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1186</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>4183</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>4,16%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1287</t>
+          <t>1334</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7559</t>
+          <t>7511</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,28%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>22101</t>
+          <t>21922</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>28049</t>
+          <t>27306</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,49 +7731,49 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
+          <t>78,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
+          <t>97,35%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>27324</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>24918</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>28510</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>95,84%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>87,4%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>27324</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>24327</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>28510</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>95,84%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>85,33%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>78</t>
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>49000</t>
+          <t>49048</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>55272</t>
+          <t>55225</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>86,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,64%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3635</t>
+          <t>3769</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12644</t>
+          <t>12784</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2536</t>
+          <t>2529</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9440</t>
+          <t>10005</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8178</t>
+          <t>7716</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18872</t>
+          <t>18602</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,02%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>87670</t>
+          <t>87530</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>96679</t>
+          <t>96545</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>87,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>122152</t>
+          <t>121587</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>129056</t>
+          <t>129063</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>213034</t>
+          <t>213304</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>223728</t>
+          <t>224190</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,67%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP18A01-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP18A01-Habitat-trans_orig.xlsx
@@ -538,13 +538,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según su última visita al médico fue por vacunación en 2007 (tasa de respuesta: 99,78%)</t>
+          <t>Menores según si su última consulta médica fue por vacunación en 2007 (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5931</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3161</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>10273</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>4,6%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2,45%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>7,96%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>4624</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1941</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>8910</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>1908</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>8685</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>4,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,68%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>7,71%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>5931</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>3176</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>10710</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>4,6%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5997</t>
+          <t>6672</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15890</t>
+          <t>17197</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>7,03%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>123066</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>118724</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>125836</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>95,4%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>92,04%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>97,55%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>161</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>110921</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>106635</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>113604</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>106860</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>113637</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>96,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>92,29%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>98,32%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>181</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>123066</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>118287</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>125821</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>95,4%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>228652</t>
+          <t>227345</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>238545</t>
+          <t>237870</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,27%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>128997</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>128997</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>128997</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>168</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>115545</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>115545</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>115545</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>128997</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>128997</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>128997</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>10389</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>6400</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>16912</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>5,77%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3,56%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>9,4%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>11223</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>6929</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>17343</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>6804</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>16957</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>6,79%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>4,19%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>10,49%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>10389</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>5983</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>15793</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>5,77%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15085</t>
+          <t>15223</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28835</t>
+          <t>29060</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,42%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>169527</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>163004</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>173516</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>94,23%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>90,6%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>96,44%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>247</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>154130</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>148010</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>158424</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>148396</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>158549</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>93,21%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>89,51%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>95,81%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>258</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>169527</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>164123</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>173933</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>94,23%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>316434</t>
+          <t>316209</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>330184</t>
+          <t>330046</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,59%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>274</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>179916</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>179916</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>179916</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>265</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>165353</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>165353</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>165353</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>274</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>179916</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>179916</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>179916</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>13261</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>8783</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>19334</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>9,91%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>6,56%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>14,45%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>13350</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>8676</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>19010</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>9130</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>19310</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>10,72%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>6,96%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>15,26%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>13261</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>8557</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>19335</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>9,91%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19868</t>
+          <t>19672</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>34879</t>
+          <t>34584</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,39%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>120535</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>114462</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>125013</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>90,09%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>85,55%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>93,44%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>184</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>111227</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>105567</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>115901</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>105267</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>115447</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>89,28%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>84,74%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>93,04%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>120535</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>114461</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>125239</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>90,09%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>84,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>223494</t>
+          <t>223789</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>238505</t>
+          <t>238701</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,5%</t>
+          <t>86,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,39%</t>
         </is>
       </c>
     </row>
@@ -1640,52 +1640,52 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>133796</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>133796</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>133796</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
           <t>124577</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>124577</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>124577</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>133796</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>133796</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>133796</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>22605</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>15605</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>30127</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>12,47%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>8,61%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>16,62%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>21930</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>15140</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>29927</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>15188</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>30701</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>11,39%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>7,86%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>15,54%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>22605</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>15598</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>30615</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>12,47%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>34926</t>
+          <t>35447</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>55814</t>
+          <t>55406</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,82%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>158701</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>151179</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>165701</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>87,53%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>83,38%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>91,39%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>223</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>170613</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>162616</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>177403</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>161842</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>177355</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>88,61%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>84,46%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>92,14%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>158701</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>150691</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>165708</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>87,53%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,11%</t>
+          <t>84,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>318034</t>
+          <t>318442</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>338922</t>
+          <t>338401</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>85,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>90,52%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>181306</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>181306</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>181306</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>252</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>192543</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>192543</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>192543</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>181306</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>181306</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>181306</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>52186</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>41097</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>63437</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>8,36%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>6,59%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>10,17%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>51127</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>42169</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>63698</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>40701</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>62933</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>8,55%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>7,05%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>10,65%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>52186</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>41648</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>64459</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>8,36%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>88837</t>
+          <t>87981</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>120141</t>
+          <t>121498</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,94%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>861</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>571828</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>560577</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>582917</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>91,64%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>89,83%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>93,41%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>815</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>546891</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>534320</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>555849</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>535085</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>557317</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>91,45%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>89,35%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>92,95%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>861</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>571828</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>559555</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>582366</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>91,64%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1101891</t>
+          <t>1100534</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1133195</t>
+          <t>1134051</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>90,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,8%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>939</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>624014</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>624014</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>624014</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>892</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>598018</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>598018</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>598018</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>939</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>624014</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>624014</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>624014</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2485,13 +2485,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según su última visita al médico fue por vacunación en 2012 (tasa de respuesta: 98,1%)</t>
+          <t>Menores según si su última consulta médica fue por vacunación en 2012 (tasa de respuesta: 98,1%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>14804</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>9004</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>21619</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>10,13%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>6,16%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>14,79%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>13541</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>7988</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>19867</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>8754</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>20947</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>10,49%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>6,19%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>15,39%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>14804</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>9181</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>21963</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>10,13%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20776</t>
+          <t>20461</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38432</t>
+          <t>37229</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,53%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>131330</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>124515</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>137130</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>89,87%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>85,21%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>93,84%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>115557</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>109231</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>121110</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>108151</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>120344</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>89,51%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>84,61%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>93,81%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>131330</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>124171</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>136953</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>89,87%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,97%</t>
+          <t>83,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>236800</t>
+          <t>238003</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>254456</t>
+          <t>254771</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>86,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,57%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>146134</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>146134</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>146134</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>175</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>129098</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>129098</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>129098</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>199</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>146134</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>146134</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>146134</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>18107</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>12120</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>25890</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>8,85%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>5,92%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>12,65%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>13300</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>8299</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>19534</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>8060</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>19751</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>6,99%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>4,36%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>10,26%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>18107</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>12091</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>26087</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>8,85%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>23358</t>
+          <t>22842</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>41197</t>
+          <t>41013</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,38%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>186517</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>178734</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>192504</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>91,15%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>87,35%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>94,08%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>273</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>177065</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>170831</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>182066</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>170614</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>182305</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>93,01%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>89,74%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>95,64%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>186517</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>178537</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>192533</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>91,15%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>89,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>353792</t>
+          <t>353976</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>371631</t>
+          <t>372147</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>89,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,22%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>295</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>204624</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>204624</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>204624</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>294</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>190365</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>190365</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>190365</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>295</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>204624</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>204624</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>204624</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3361,67 +3361,67 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>14042</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>8738</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>21255</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>9,02%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>5,62%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>13,66%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>12337</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>7930</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>18422</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>7984</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>18125</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>8,68%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>5,58%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>12,97%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>14042</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>8939</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>21275</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>9,02%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20072</t>
+          <t>19176</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>34925</t>
+          <t>35409</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,9%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>141553</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>134340</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>146857</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>90,98%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>86,34%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>94,38%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>201</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>129726</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>123641</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>134133</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>123938</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>134079</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>91,32%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>87,03%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>94,42%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>218</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>141553</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>134320</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>146656</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>90,98%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>87,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>262733</t>
+          <t>262249</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>277586</t>
+          <t>278482</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,27%</t>
+          <t>88,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,56%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>155595</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>155595</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>155595</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>221</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>142063</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>142063</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>142063</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>155595</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>155595</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>155595</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3704,67 +3704,67 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>23866</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>17249</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>31888</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>11,86%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>8,57%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>15,84%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>25931</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>18549</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>35401</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>18217</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>34744</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>12,82%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>9,17%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>17,5%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>23866</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>16890</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>31987</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>11,86%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>38874</t>
+          <t>39601</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>62497</t>
+          <t>63271</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,68%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>177443</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>169421</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>184060</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>88,14%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>84,16%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>91,43%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>232</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>176347</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>166877</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>183729</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>167534</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>184061</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>87,18%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>82,5%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>90,83%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>177443</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>169322</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>184419</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>88,14%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,11%</t>
+          <t>82,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>341089</t>
+          <t>340315</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>364712</t>
+          <t>363985</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>84,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,19%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>201309</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>201309</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>201309</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>265</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>202278</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>202278</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>202278</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>201309</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>201309</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>201309</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>70819</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>58462</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>87104</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>10,01%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>8,26%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>12,31%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>65108</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>53923</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>77796</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>52968</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>78747</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>9,81%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>8,12%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>11,72%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>70819</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>58366</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>85503</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>10,01%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>119009</t>
+          <t>118088</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>155819</t>
+          <t>153873</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,22%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>907</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>636842</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>620557</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>649199</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>89,99%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>87,69%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>91,74%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>862</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>598696</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>586008</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>609881</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>585057</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>610836</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>90,19%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>88,28%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>91,88%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>907</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>636842</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>622158</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>649295</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>89,99%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>88,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1215646</t>
+          <t>1217592</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1252456</t>
+          <t>1253377</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>88,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,39%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>707661</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>707661</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>707661</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>955</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>663804</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>663804</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>663804</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1005</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>707661</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>707661</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>707661</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4432,13 +4432,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según su última visita al médico fue por vacunación en 2016 (tasa de respuesta: 98,16%)</t>
+          <t>Menores según si su última consulta médica fue por vacunación en 2016 (tasa de respuesta: 98,16%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4622,67 +4622,67 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>12462</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7343</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>19209</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>9,21%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>5,43%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>14,19%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>12301</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>6990</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>18788</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>7750</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>19049</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>10,02%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>5,69%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>15,3%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>12462</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>7629</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>19007</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>9,21%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17616</t>
+          <t>16996</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33983</t>
+          <t>32857</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>12,73%</t>
         </is>
       </c>
     </row>
@@ -4730,72 +4730,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>122877</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>116130</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>127996</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>90,79%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>85,81%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>94,57%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>154</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>110520</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>104033</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>115831</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>103772</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>115071</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>89,98%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>84,7%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>94,31%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>122877</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>116332</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>127710</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>90,79%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>84,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>224177</t>
+          <t>225303</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>240544</t>
+          <t>241164</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>87,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,42%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>135339</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>135339</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>135339</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>171</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>122821</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>122821</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>122821</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>135339</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>135339</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>135339</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>18306</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>12900</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>26345</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>8,77%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>6,18%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>12,62%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>14531</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>9142</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>20330</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>9334</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>21092</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>7,52%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>4,73%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>10,52%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>18306</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>12888</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>26325</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>8,77%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>24978</t>
+          <t>25127</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>41730</t>
+          <t>42016</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,45%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>190424</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>182385</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>195830</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>91,23%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>87,38%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>93,82%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>287</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>178787</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>172988</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>184176</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>172226</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>183984</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>92,48%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>89,48%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>95,27%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>190424</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>182405</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>195842</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>91,23%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>360318</t>
+          <t>360032</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>377070</t>
+          <t>376921</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>89,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,75%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>208730</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>208730</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>208730</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>311</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>193318</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>193318</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>193318</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>309</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>208730</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>208730</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>208730</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>11752</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6916</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>18088</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>8,2%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>4,83%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>12,62%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>12392</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>7948</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>19194</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>7556</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>18244</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>9,11%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>5,84%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>14,11%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>11752</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>6619</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>17873</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>8,2%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16982</t>
+          <t>16796</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>32225</t>
+          <t>33177</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,88%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>131521</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>125185</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>136357</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>91,8%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>87,38%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>95,17%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>207</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>123608</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>116806</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>128052</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>117756</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>128444</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>90,89%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>85,89%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>94,16%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>131521</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>125400</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>136654</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>91,8%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>86,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>247048</t>
+          <t>246096</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>262291</t>
+          <t>262477</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>88,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>93,99%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>143273</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>143273</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>143273</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>227</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>136000</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>136000</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>136000</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>143273</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>143273</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>143273</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>10577</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>23696</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>8,83%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>5,8%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>13,0%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>21024</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>14080</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>29003</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>14015</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>28837</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>11,17%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>7,48%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>15,41%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>16101</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>10735</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>23266</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>8,83%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>27951</t>
+          <t>27745</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>46624</t>
+          <t>49638</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>13,4%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>166238</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>158643</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>171762</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>91,17%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>87,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>94,2%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>167181</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>159202</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>174125</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>159368</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>174190</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>88,83%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>84,59%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>92,52%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>166238</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>159073</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>171604</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>91,17%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,24%</t>
+          <t>84,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>323920</t>
+          <t>320906</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>342593</t>
+          <t>342799</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>86,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,51%</t>
         </is>
       </c>
     </row>
@@ -5877,52 +5877,52 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>182339</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>182339</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>182339</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
           <t>188205</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>188205</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>188205</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>256</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>182339</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>182339</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>182339</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>58621</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>45971</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>72075</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>8,75%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>6,86%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>10,76%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>60248</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>49014</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>74082</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>49663</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>72997</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>9,41%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>7,65%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>11,57%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>58621</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>47953</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>72760</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>8,75%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>102758</t>
+          <t>103583</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>135141</t>
+          <t>137035</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,46%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>874</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>611060</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>597606</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>623710</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>91,25%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>89,24%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>93,14%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>877</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>580097</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>566263</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>591331</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>567348</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>590682</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>90,59%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>88,43%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>92,35%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>874</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>611060</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>596921</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>621728</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>91,25%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1174884</t>
+          <t>1172990</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1207267</t>
+          <t>1206442</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,09%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>957</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>669681</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>669681</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>669681</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>965</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>640345</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>640345</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>640345</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>957</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>669681</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>669681</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>669681</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6379,13 +6379,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según su última visita al médico fue por vacunación en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según si su última consulta médica fue por vacunación en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,107 +6564,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1283</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1282</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4602</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>7,52%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4795</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>7,48%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>26,98%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>27,97%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1282</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>5131</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>3,45%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1283</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>5576</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>3,31%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>13,8%</t>
         </is>
       </c>
     </row>
@@ -6677,74 +6677,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>20043</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>15771</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>12452</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>17054</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>92,48%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>73,02%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>15862</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>12349</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>17144</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>92,52%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>72,03%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>21666</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>59</t>
@@ -6752,27 +6752,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>37437</t>
+          <t>35905</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>33144</t>
+          <t>32056</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>38720</t>
+          <t>37187</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>20043</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>20043</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>20043</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>17054</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>17054</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>17054</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>21666</t>
+          <t>17144</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>21666</t>
+          <t>17144</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>21666</t>
+          <t>17144</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>38720</t>
+          <t>37187</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>38720</t>
+          <t>37187</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>38720</t>
+          <t>37187</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3273</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1214</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>6801</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>7,21%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2,67%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>14,98%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>2341</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>773</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>5784</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>8,08%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2,67%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>19,96%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3761</t>
+          <t>2182</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1611</t>
+          <t>711</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7357</t>
+          <t>5386</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>6102</t>
+          <t>5454</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3223</t>
+          <t>2924</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10568</t>
+          <t>9756</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,49%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>42120</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>38592</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>44179</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>92,79%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>85,02%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>97,33%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>26634</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>23191</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>28202</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>91,92%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>80,04%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>97,33%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>45975</t>
+          <t>24767</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>42379</t>
+          <t>21563</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>48125</t>
+          <t>26238</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,21%</t>
+          <t>80,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>72609</t>
+          <t>66888</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>68143</t>
+          <t>62586</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>75488</t>
+          <t>69418</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>86,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,96%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>45393</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>45393</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>45393</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>28975</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>28975</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>28975</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>49736</t>
+          <t>26949</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>49736</t>
+          <t>26949</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>49736</t>
+          <t>26949</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>78711</t>
+          <t>72342</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>78711</t>
+          <t>72342</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>78711</t>
+          <t>72342</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>298</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1571</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,99%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>5,2%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>1231</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1048</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4259</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>4,69%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>4345</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>4,42%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>16,23%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>396</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>2234</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1627</t>
+          <t>1347</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>298</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4814</t>
+          <t>4133</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>7,67%</t>
         </is>
       </c>
     </row>
@@ -7363,74 +7363,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>29885</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>28612</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>30183</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,01%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>94,8%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>25005</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>21977</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>26236</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>95,31%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>83,77%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>22670</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>19373</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>23718</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>95,58%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>81,68%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>31284</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>29446</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>31680</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>98,75%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>92,95%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>74</t>
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>56290</t>
+          <t>52554</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>53103</t>
+          <t>49768</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>57541</t>
+          <t>53603</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,45%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>30183</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>30183</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>30183</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>26236</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>26236</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>26236</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>31680</t>
+          <t>23718</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>31680</t>
+          <t>23718</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>31680</t>
+          <t>23718</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>57917</t>
+          <t>53901</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>57917</t>
+          <t>53901</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>57917</t>
+          <t>53901</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>977</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3467</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3,74%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>13,28%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>2305</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>743</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>6127</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>8,22%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2,65%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>21,84%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1186</t>
+          <t>2326</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>720</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3592</t>
+          <t>5609</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>3491</t>
+          <t>3303</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1334</t>
+          <t>1205</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7511</t>
+          <t>7092</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,18%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>25744</t>
+          <t>25126</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>21922</t>
+          <t>22636</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>27306</t>
+          <t>26103</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,16%</t>
+          <t>86,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>27324</t>
+          <t>25375</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>24918</t>
+          <t>22092</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>28510</t>
+          <t>26981</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>79,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>53068</t>
+          <t>50501</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>49048</t>
+          <t>46712</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>55225</t>
+          <t>52599</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,72%</t>
+          <t>86,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,76%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>26103</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>26103</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>26103</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>28049</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>28049</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>28049</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>28510</t>
+          <t>27701</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>28510</t>
+          <t>27701</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>28510</t>
+          <t>27701</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>56559</t>
+          <t>53804</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>56559</t>
+          <t>53804</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>56559</t>
+          <t>53804</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>4549</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2282</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>8806</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>3,74%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1,87%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>7,23%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>7160</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>3769</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>12784</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>7,14%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>3,76%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>12,74%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>5343</t>
+          <t>6838</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2529</t>
+          <t>3298</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10005</t>
+          <t>12315</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>12503</t>
+          <t>11387</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7716</t>
+          <t>7286</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18602</t>
+          <t>17885</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,23%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>117173</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>112916</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>119440</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>96,26%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>92,77%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>98,13%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>141</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>93154</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>87530</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>96545</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>92,86%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>87,26%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>96,24%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>126249</t>
+          <t>88674</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>121587</t>
+          <t>83197</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>129063</t>
+          <t>92214</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>87,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>219403</t>
+          <t>205847</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>213304</t>
+          <t>199349</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>224190</t>
+          <t>209948</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>91,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,65%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>121722</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>121722</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>121722</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>153</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>100314</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>100314</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>100314</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>131592</t>
+          <t>95512</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>131592</t>
+          <t>95512</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>131592</t>
+          <t>95512</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>231906</t>
+          <t>217234</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>231906</t>
+          <t>217234</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>231906</t>
+          <t>217234</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
